--- a/XLSX/Igloo.xlsx
+++ b/XLSX/Igloo.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAFBD5-E30F-0443-820F-01C3A6A99F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65980A63-9156-478A-9290-4F6F0CC57AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19460" yWindow="780" windowWidth="10000" windowHeight="19100" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="6405" windowHeight="17385" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="5">
   <si>
     <t>nummer</t>
   </si>
@@ -48,6 +51,12 @@
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>/tp</t>
+  </si>
+  <si>
+    <t>~</t>
   </si>
 </sst>
 </file>
@@ -426,30 +435,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>-456</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>-968</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>-200</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>-1176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>4760</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>-1720</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>4360</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>-1336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5144</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>-1896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4360</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>-232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>3160</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>2760</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>-824</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4472</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>4808</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>-3432</v>
+      </c>
+      <c r="D12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>5816</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>-3768</v>
+      </c>
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>5832</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>-4232</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>5848</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>-3032</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>5176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>-3272</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>4952</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:E1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
